--- a/voting/015_member_selection_ranking_survey--voting.xlsx
+++ b/voting/015_member_selection_ranking_survey--voting.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'a',_'label':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 'A', 'label': 'A'}</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'b',_'label':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 'B', 'label': 'B'}</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'c',_'label':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 'C', 'label': 'C'}</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'d',_'label':_'d'}</t>
+          <t>d</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 'D', 'label': 'D'}</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'e',_'label':_'e'}</t>
+          <t>e</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 'E', 'label': 'E'}</t>
+          <t>E</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'new',_'label':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 'New', 'label': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'in_progress',_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 'In Progress', 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'completed',_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 'Completed', 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
